--- a/data/trans_orig/P36BPD13_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD13_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas en 2023</t>
+          <t>Población según si consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas en 2023 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>287196</t>
+          <t>286461</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>302793</t>
+          <t>302330</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>281964</t>
+          <t>281836</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>287722</t>
+          <t>287714</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>572891</t>
+          <t>571547</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>589034</t>
+          <t>589163</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7118</t>
+          <t>7581</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22715</t>
+          <t>23450</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>7799</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10512</t>
+          <t>10383</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>27999</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>290204</t>
+          <t>288093</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>346953</t>
+          <t>345706</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>371570</t>
+          <t>372764</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>405777</t>
+          <t>406855</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>674159</t>
+          <t>673693</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>740410</t>
+          <t>743915</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>72,12%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>170161</t>
+          <t>171408</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>226910</t>
+          <t>229021</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>108533</t>
+          <t>107455</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>142740</t>
+          <t>141546</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>291015</t>
+          <t>287510</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>357266</t>
+          <t>357732</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,68%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>248136</t>
+          <t>249474</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>273965</t>
+          <t>274581</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>299734</t>
+          <t>300188</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>318234</t>
+          <t>318619</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>557810</t>
+          <t>557943</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>588348</t>
+          <t>588136</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,59%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34003</t>
+          <t>33387</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59832</t>
+          <t>58494</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23015</t>
+          <t>22630</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41515</t>
+          <t>41061</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60869</t>
+          <t>61081</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>91407</t>
+          <t>91274</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>263452</t>
+          <t>263183</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>290164</t>
+          <t>289172</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>440192</t>
+          <t>440699</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>459991</t>
+          <t>459526</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>709758</t>
+          <t>711309</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>745827</t>
+          <t>747550</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20098</t>
+          <t>21090</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46810</t>
+          <t>47079</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12459</t>
+          <t>12924</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32258</t>
+          <t>31751</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36885</t>
+          <t>35162</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>72954</t>
+          <t>71403</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>168821</t>
+          <t>169036</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>176300</t>
+          <t>176556</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>192159</t>
+          <t>191579</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>201630</t>
+          <t>201619</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>365170</t>
+          <t>365001</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>376621</t>
+          <t>376564</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9248</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15364</t>
+          <t>15944</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8971</t>
+          <t>9028</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20422</t>
+          <t>20591</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>239613</t>
+          <t>239521</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>255932</t>
+          <t>256344</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>241017</t>
+          <t>240983</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>251525</t>
+          <t>251148</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>486702</t>
+          <t>486333</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>504950</t>
+          <t>505225</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,08%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12826</t>
+          <t>12414</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29145</t>
+          <t>29237</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5531</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16039</t>
+          <t>16073</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20863</t>
+          <t>20588</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39111</t>
+          <t>39480</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>467368</t>
+          <t>466757</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>513225</t>
+          <t>513244</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>661304</t>
+          <t>663350</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>778076</t>
+          <t>776408</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1150360</t>
+          <t>1149250</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1304501</t>
+          <t>1303662</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,44%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>107566</t>
+          <t>107547</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>153423</t>
+          <t>154034</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>58715</t>
+          <t>60383</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>175487</t>
+          <t>173441</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>153081</t>
+          <t>153920</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>307222</t>
+          <t>308332</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>835782</t>
+          <t>835641</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>898817</t>
+          <t>896943</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>621930</t>
+          <t>621481</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>652995</t>
+          <t>651833</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1470621</t>
+          <t>1471576</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1556355</t>
+          <t>1558131</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>28166</t>
+          <t>30040</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>91201</t>
+          <t>91342</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>63382</t>
+          <t>64544</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>94447</t>
+          <t>94896</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>87005</t>
+          <t>85229</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>172739</t>
+          <t>171784</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2875657</t>
+          <t>2868463</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3044662</t>
+          <t>3037284</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3189337</t>
+          <t>3188872</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3307672</t>
+          <t>3303712</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6087588</t>
+          <t>6088937</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6310817</t>
+          <t>6286971</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>88,86%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>395194</t>
+          <t>402572</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>564199</t>
+          <t>571393</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>327718</t>
+          <t>331678</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>446053</t>
+          <t>446518</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>764429</t>
+          <t>788275</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>987658</t>
+          <t>986309</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD13_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD13_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>296726</t>
+          <t>306361</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>286461</t>
+          <t>298020</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>302330</t>
+          <t>311601</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>285484</t>
+          <t>310833</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>281836</t>
+          <t>306341</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>287714</t>
+          <t>313475</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>582210</t>
+          <t>617194</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>571547</t>
+          <t>608347</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>589163</t>
+          <t>622962</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13185</t>
+          <t>11247</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7581</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23450</t>
+          <t>19588</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>5228</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>2586</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7799</t>
+          <t>9720</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>17336</t>
+          <t>16475</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10383</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27999</t>
+          <t>25322</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>309911</t>
+          <t>317608</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>309911</t>
+          <t>317608</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>309911</t>
+          <t>317608</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>599546</t>
+          <t>633669</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>599546</t>
+          <t>633669</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>599546</t>
+          <t>633669</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>318128</t>
+          <t>325268</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>288093</t>
+          <t>297647</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>345706</t>
+          <t>350226</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>390505</t>
+          <t>410827</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>372764</t>
+          <t>390420</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>406855</t>
+          <t>428721</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>708634</t>
+          <t>736095</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>673693</t>
+          <t>700816</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>743915</t>
+          <t>768660</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>71,49%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>198986</t>
+          <t>204093</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>171408</t>
+          <t>179135</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>229021</t>
+          <t>231714</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>123805</t>
+          <t>134984</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>107455</t>
+          <t>117090</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>141546</t>
+          <t>155391</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>322791</t>
+          <t>339077</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>287510</t>
+          <t>306512</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>357732</t>
+          <t>374356</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,82%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517114</t>
+          <t>529361</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517114</t>
+          <t>529361</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517114</t>
+          <t>529361</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514310</t>
+          <t>545811</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514310</t>
+          <t>545811</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514310</t>
+          <t>545811</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031425</t>
+          <t>1075172</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031425</t>
+          <t>1075172</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031425</t>
+          <t>1075172</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>263453</t>
+          <t>262457</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>249474</t>
+          <t>250348</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>274581</t>
+          <t>274844</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>310675</t>
+          <t>316504</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>300188</t>
+          <t>305592</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>318619</t>
+          <t>324817</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,22 +1481,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>574128</t>
+          <t>578961</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>557943</t>
+          <t>563405</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>588136</t>
+          <t>594211</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,64%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44515</t>
+          <t>45553</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33387</t>
+          <t>33166</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58494</t>
+          <t>57662</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30574</t>
+          <t>31068</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22630</t>
+          <t>22755</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41061</t>
+          <t>41980</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,27 +1594,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>75089</t>
+          <t>76621</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61081</t>
+          <t>61371</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>91274</t>
+          <t>92177</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>307968</t>
+          <t>308010</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>307968</t>
+          <t>308010</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>307968</t>
+          <t>308010</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>341249</t>
+          <t>347572</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>341249</t>
+          <t>347572</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>341249</t>
+          <t>347572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>649217</t>
+          <t>655582</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>649217</t>
+          <t>655582</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>649217</t>
+          <t>655582</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>278413</t>
+          <t>331623</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>263183</t>
+          <t>314046</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>289172</t>
+          <t>344430</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>450301</t>
+          <t>392894</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>440699</t>
+          <t>383723</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>459526</t>
+          <t>399593</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>728714</t>
+          <t>724516</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>711309</t>
+          <t>704770</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>747550</t>
+          <t>741074</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>31849</t>
+          <t>38887</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21090</t>
+          <t>26080</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47079</t>
+          <t>56464</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>22149</t>
+          <t>25564</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12924</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31751</t>
+          <t>34735</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>53998</t>
+          <t>64451</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35162</t>
+          <t>47893</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>71403</t>
+          <t>84197</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>310262</t>
+          <t>370510</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>310262</t>
+          <t>370510</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>310262</t>
+          <t>370510</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>472450</t>
+          <t>418458</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>472450</t>
+          <t>418458</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>472450</t>
+          <t>418458</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>782712</t>
+          <t>788967</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>782712</t>
+          <t>788967</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>782712</t>
+          <t>788967</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>173856</t>
+          <t>200292</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>169036</t>
+          <t>195354</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>176556</t>
+          <t>202869</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>198036</t>
+          <t>215926</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>191579</t>
+          <t>210747</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>201619</t>
+          <t>219523</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>371892</t>
+          <t>416217</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>365001</t>
+          <t>409994</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>376564</t>
+          <t>421108</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9033</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>6520</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15944</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>13700</t>
+          <t>14760</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9028</t>
+          <t>9869</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20591</t>
+          <t>20983</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178069</t>
+          <t>204934</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178069</t>
+          <t>204934</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178069</t>
+          <t>204934</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207523</t>
+          <t>226043</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207523</t>
+          <t>226043</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207523</t>
+          <t>226043</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>385592</t>
+          <t>430977</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>385592</t>
+          <t>430977</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>385592</t>
+          <t>430977</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,22 +2440,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>249338</t>
+          <t>250619</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>239521</t>
+          <t>240521</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>256344</t>
+          <t>256922</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>247441</t>
+          <t>254232</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>240983</t>
+          <t>248479</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>251148</t>
+          <t>257912</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>496778</t>
+          <t>504851</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>486333</t>
+          <t>494635</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>505225</t>
+          <t>513477</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -2553,27 +2553,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>19420</t>
+          <t>19276</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12414</t>
+          <t>12973</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29237</t>
+          <t>29374</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9615</t>
+          <t>9518</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16073</t>
+          <t>15271</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>29035</t>
+          <t>28794</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20588</t>
+          <t>20168</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39480</t>
+          <t>39010</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>268758</t>
+          <t>269895</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>268758</t>
+          <t>269895</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>268758</t>
+          <t>269895</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>525813</t>
+          <t>533645</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>525813</t>
+          <t>533645</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>525813</t>
+          <t>533645</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>491666</t>
+          <t>570928</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>466757</t>
+          <t>546419</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>513244</t>
+          <t>597018</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>712357</t>
+          <t>609092</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>663350</t>
+          <t>588407</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>776408</t>
+          <t>628430</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1204022</t>
+          <t>1180020</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1149250</t>
+          <t>1145823</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1303662</t>
+          <t>1208162</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>82,04%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>129125</t>
+          <t>144115</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>107547</t>
+          <t>118025</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>154034</t>
+          <t>168624</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>124434</t>
+          <t>148493</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>60383</t>
+          <t>129155</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>173441</t>
+          <t>169178</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>253560</t>
+          <t>292609</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>153920</t>
+          <t>264467</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>308332</t>
+          <t>326806</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>620791</t>
+          <t>715043</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>620791</t>
+          <t>715043</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>620791</t>
+          <t>715043</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>836791</t>
+          <t>757585</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>836791</t>
+          <t>757585</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>836791</t>
+          <t>757585</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1457582</t>
+          <t>1472629</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1457582</t>
+          <t>1472629</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1457582</t>
+          <t>1472629</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>865026</t>
+          <t>720829</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>835641</t>
+          <t>701430</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>896943</t>
+          <t>736249</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>638858</t>
+          <t>741392</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>621481</t>
+          <t>724646</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>651833</t>
+          <t>757977</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1503884</t>
+          <t>1462221</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1471576</t>
+          <t>1436499</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1558131</t>
+          <t>1483934</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>91,26%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>61957</t>
+          <t>75325</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>30040</t>
+          <t>59905</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>91342</t>
+          <t>94724</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>77519</t>
+          <t>88445</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>64544</t>
+          <t>71860</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>94896</t>
+          <t>105191</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>139476</t>
+          <t>163770</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>85229</t>
+          <t>142057</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>171784</t>
+          <t>189492</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>926983</t>
+          <t>796154</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>926983</t>
+          <t>796154</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>926983</t>
+          <t>796154</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>716377</t>
+          <t>829837</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>716377</t>
+          <t>829837</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>716377</t>
+          <t>829837</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1643360</t>
+          <t>1625991</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1643360</t>
+          <t>1625991</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1643360</t>
+          <t>1625991</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2936605</t>
+          <t>2968376</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2868463</t>
+          <t>2919385</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3037284</t>
+          <t>3018999</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3233657</t>
+          <t>3251699</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3188872</t>
+          <t>3216731</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3303712</t>
+          <t>3288283</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>6170262</t>
+          <t>6220076</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6088937</t>
+          <t>6159518</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6286971</t>
+          <t>6280462</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>87,03%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>503251</t>
+          <t>543139</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>402572</t>
+          <t>492516</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>571393</t>
+          <t>592130</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>401733</t>
+          <t>453418</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>331678</t>
+          <t>416834</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>446518</t>
+          <t>488386</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>904984</t>
+          <t>996556</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>788275</t>
+          <t>936170</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>986309</t>
+          <t>1057114</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3439856</t>
+          <t>3511515</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3439856</t>
+          <t>3511515</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3439856</t>
+          <t>3511515</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3635390</t>
+          <t>3705117</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3635390</t>
+          <t>3705117</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3635390</t>
+          <t>3705117</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7075246</t>
+          <t>7216632</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7075246</t>
+          <t>7216632</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7075246</t>
+          <t>7216632</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
